--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLII/LTAIPT_A63F42A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLII/LTAIPT_A63F42A.xlsx
@@ -109,16 +109,16 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>AD59E44D7EC39529B84B33015565B266</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>5443E62BCA2EFA2D24067A1693A97AF5</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>El listado de jubilados y pensionados es generado y publicado por el Instituto de Seguridad Social al Servicio de los Trabajadores del Estado como parte de las prestaciones de Ley que derivan del esquema de Seguridad Social previsto en la Ley del Instituto de Seguridad Social al Servicio de los Trabajadores del Estado, toda vez que el Colegio de Bachilleres del Estado de Tlaxcala no tiene un esquema propio de jubilaciones y pensiones.</t>
@@ -130,7 +130,7 @@
     <t>Departamento de Recursos Humanos</t>
   </si>
   <si>
-    <t>13/01/2023</t>
+    <t>17/04/2023</t>
   </si>
   <si>
     <t/>
@@ -529,7 +529,7 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
